--- a/05-项目管理/02-进度管理/01-项目甘特图模板.xlsx
+++ b/05-项目管理/02-进度管理/01-项目甘特图模板.xlsx
@@ -93,7 +93,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -120,11 +120,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +157,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +541,13 @@
           <t>01-项目甘特图模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -539,6 +555,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -546,6 +563,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -553,6 +571,9 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -560,6 +581,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -567,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -574,6 +597,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -581,6 +605,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -616,6 +641,9 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -623,6 +651,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
@@ -630,6 +659,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
@@ -637,6 +667,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
@@ -644,6 +675,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -651,6 +683,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
@@ -658,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
@@ -665,6 +699,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
@@ -672,6 +707,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
@@ -679,6 +715,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
@@ -686,6 +723,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
@@ -693,6 +731,9 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
@@ -700,6 +741,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -707,6 +749,9 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -714,6 +759,7 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
@@ -721,6 +767,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
@@ -742,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
@@ -749,6 +797,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
@@ -777,6 +826,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
@@ -784,6 +834,7 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
@@ -805,6 +856,9 @@
         </is>
       </c>
     </row>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
@@ -812,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
@@ -852,8 +907,8 @@
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A75:F75"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A75:F75"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A3:F3"/>
@@ -1015,17 +1070,17 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>某型号</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1194,32 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>M7</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>某型号</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1392,47 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>M13</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>M14</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>M15</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>M16</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>M17</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>M18</t>
+          <t>某型号</t>
         </is>
       </c>
     </row>
@@ -1647,62 +1702,62 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>M19</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>M20</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>M21</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>M22</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>M23</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>M25</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>M26</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>M27</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>M28</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>M29</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>M30</t>
+          <t>某型号</t>
         </is>
       </c>
     </row>
@@ -1951,32 +2006,32 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>M32</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>M33</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>M34</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>M35</t>
+          <t>某型号</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>M36</t>
+          <t>某型号</t>
         </is>
       </c>
     </row>
